--- a/Models/Верблюды/results/Верблюды - Результаты прогнозов ХВ.xlsx
+++ b/Models/Верблюды/results/Верблюды - Результаты прогнозов ХВ.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,17 +478,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[-0.11, -0.05, 0.04]</t>
+          <t>[0.15, -0.04, -0.09]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.07144285366496693</v>
+        <v>0.1026227825171762</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06484504976718401</v>
+        <v>0.09371860670485814</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -516,17 +516,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[-0.05, 0.04, -0.04]</t>
+          <t>[-0.05, -0.1, 0.08]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.04453193491183231</v>
+        <v>0.07836179879272508</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04448494521425483</v>
+        <v>0.07561684073788806</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -554,17 +554,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[0.04, -0.04, -0.08]</t>
+          <t>[-0.1, 0.08, 0.36]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.05815457290881464</v>
+        <v>0.2222640272178255</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05551950065065508</v>
+        <v>0.1805269204833102</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -592,17 +592,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[-0.04, -0.08, 0.3]</t>
+          <t>[0.09, 0.37, -0.09]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -611,10 +611,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.1836100653736649</v>
+        <v>0.2260617581486191</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1433770650005885</v>
+        <v>0.1831617125988631</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -630,17 +630,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[-0.08, 0.31, -0.05]</t>
+          <t>[0.37, -0.1, -0.05]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.1855338081348277</v>
+        <v>0.2197842377848225</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1458166865786563</v>
+        <v>0.1699641964365922</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -668,17 +668,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[0.31, -0.05, 0.16]</t>
+          <t>[-0.11, -0.06, 0.02]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -687,10 +687,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.2037463359797968</v>
+        <v>0.07402464939213607</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1719959998090861</v>
+        <v>0.06304035940969692</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -706,17 +706,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[-0.06, 0.14, -0.05]</t>
+          <t>[-0.06, 0.02, -0.05]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.09238701801801755</v>
+        <v>0.04758791633727523</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08215577662754379</v>
+        <v>0.04470676851040572</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -744,17 +744,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[0.15, -0.04, -0.09]</t>
+          <t>[0.02, -0.05, -0.09]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.1026227825171762</v>
+        <v>0.0596516704668753</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09371860670485814</v>
+        <v>0.05416883720097136</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -782,17 +782,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[-0.05, -0.1, 0.08]</t>
+          <t>[-0.05, -0.09, 0.25]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.07836179879272508</v>
+        <v>0.1572278182556739</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07561684073788806</v>
+        <v>0.1308223036780985</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -820,17 +820,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[-0.1, 0.08, 0.36]</t>
+          <t>[-0.08, 0.26, -0.06]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2222640272178255</v>
+        <v>0.1590494635292779</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1805269204833102</v>
+        <v>0.1327174346409173</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -858,32 +858,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[114.52, 67.45, 376.0]</t>
+          <t>[5.8, 50.3, 63.88]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>[119.5, 72.6, 391.0]</t>
+          <t>[5.7, 49.87, 63.0]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9.596413476505617</v>
+        <v>0.5683608429508489</v>
       </c>
       <c r="G12" t="n">
-        <v>8.37556300219083</v>
+        <v>0.4700371255066521</v>
       </c>
       <c r="H12" t="n">
-        <v>5.031902173662442</v>
+        <v>1.344666206828437</v>
       </c>
     </row>
     <row r="13">
@@ -894,32 +894,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[67.78, 377.82, 119.42]</t>
+          <t>[50.19, 63.75, 156.25]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[72.6, 391.0, 126.1]</t>
+          <t>[49.87, 63.0, 154.3]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8.974054453642513</v>
+        <v>1.220654760929279</v>
       </c>
       <c r="G13" t="n">
-        <v>8.227851701807216</v>
+        <v>1.007066688023616</v>
       </c>
       <c r="H13" t="n">
-        <v>5.103685405129264</v>
+        <v>1.032549343742011</v>
       </c>
     </row>
     <row r="14">
@@ -930,32 +930,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[380.85, 120.38, 222.53]</t>
+          <t>[63.7, 156.12, 550.61]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>[391.0, 126.1, 229.1]</t>
+          <t>[63.0, 154.3, 538.4]</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.724536206223251</v>
+        <v>7.139774894720988</v>
       </c>
       <c r="G14" t="n">
-        <v>7.482124861736087</v>
+        <v>4.909956177012172</v>
       </c>
       <c r="H14" t="n">
-        <v>3.33426401723089</v>
+        <v>1.517769429131784</v>
       </c>
     </row>
     <row r="15">
@@ -966,32 +966,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[120.77, 223.24, 11.88]</t>
+          <t>[155.91, 549.86, 122.95]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[126.1, 229.1, 12.2]</t>
+          <t>[154.3, 538.4, 129.3]</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4.579465988325468</v>
+        <v>7.622125579556557</v>
       </c>
       <c r="G15" t="n">
-        <v>3.838816092220831</v>
+        <v>6.474373979315199</v>
       </c>
       <c r="H15" t="n">
-        <v>3.139227239455606</v>
+        <v>2.695254580355976</v>
       </c>
     </row>
     <row r="16">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[224.42, 11.95, 21.8]</t>
+          <t>[549.15, 122.79, 73.99]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>[229.1, 12.2, 24.1]</t>
+          <t>[538.4, 129.3, 77.6]</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.011993757172137</v>
+        <v>7.55189601041572</v>
       </c>
       <c r="G16" t="n">
-        <v>2.408482155805451</v>
+        <v>6.95874650517958</v>
       </c>
       <c r="H16" t="n">
-        <v>4.543908213522374</v>
+        <v>3.895247603209105</v>
       </c>
     </row>
     <row r="17">
@@ -1038,32 +1038,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[11.98, 21.86, 5.71]</t>
+          <t>[122.49, 73.81, 396.22]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>[12.2, 24.1, 5.7]</t>
+          <t>[129.3, 77.6, 411.5]</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.297838235781218</v>
+        <v>9.905105927059251</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8202641733903885</v>
+        <v>8.62798368951818</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7223935201176</v>
+        <v>4.621687798045615</v>
       </c>
     </row>
     <row r="18">
@@ -1074,32 +1074,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[21.91, 5.72, 49.69]</t>
+          <t>[74.3, 398.83, 127.97]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[24.1, 5.7, 49.87]</t>
+          <t>[77.6, 411.5, 128.1]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.267970812048417</v>
+        <v>7.559877745014761</v>
       </c>
       <c r="G18" t="n">
-        <v>0.79734352626462</v>
+        <v>5.365217488145603</v>
       </c>
       <c r="H18" t="n">
-        <v>3.267033140973494</v>
+        <v>2.475863872424277</v>
       </c>
     </row>
     <row r="19">
@@ -1110,32 +1110,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[5.8, 50.3, 63.88]</t>
+          <t>[400.93, 128.65, 233.14]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[5.7, 49.87, 63.0]</t>
+          <t>[411.5, 128.1, 235.7]</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.5683608429508489</v>
+        <v>6.287703214209606</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4700371255066521</v>
+        <v>4.5599756555447</v>
       </c>
       <c r="H19" t="n">
-        <v>1.344666206828437</v>
+        <v>1.361325247921676</v>
       </c>
     </row>
     <row r="20">
@@ -1146,32 +1146,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[50.19, 63.75, 156.25]</t>
+          <t>[129.06, 233.89, 12.45]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[49.87, 63.0, 154.3]</t>
+          <t>[128.1, 235.7, 12.2]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.220654760929279</v>
+        <v>1.193469852929088</v>
       </c>
       <c r="G20" t="n">
-        <v>1.007066688023616</v>
+        <v>1.007875569532063</v>
       </c>
       <c r="H20" t="n">
-        <v>1.032549343742011</v>
+        <v>1.184877975774724</v>
       </c>
     </row>
     <row r="21">
@@ -1182,32 +1182,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[63.7, 156.12, 550.61]</t>
+          <t>[233.67, 12.44, 24.27]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[63.0, 154.3, 538.4]</t>
+          <t>[235.7, 12.2, 25.17]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7.139774894720988</v>
+        <v>1.288150699297392</v>
       </c>
       <c r="G21" t="n">
-        <v>4.909956177012172</v>
+        <v>1.055374667458985</v>
       </c>
       <c r="H21" t="n">
-        <v>1.517769429131784</v>
+        <v>2.128481253049487</v>
       </c>
     </row>
     <row r="22">
@@ -1218,32 +1218,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>[12.54, 7.38, 31.79]</t>
+          <t>[7.06, 17.95, 5.38]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>[18.9, 17.4, 12.5]</t>
+          <t>[24.0, 7.7, 6.9]</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>13.07406258972097</v>
+        <v>11.46261073616588</v>
       </c>
       <c r="G22" t="n">
-        <v>11.88747177541902</v>
+        <v>9.568096086748227</v>
       </c>
       <c r="H22" t="n">
-        <v>81.83706771328039</v>
+        <v>75.22730360773036</v>
       </c>
     </row>
     <row r="23">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[7.38, 31.79, 6.16]</t>
+          <t>[17.95, 5.38, 6.94]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[17.4, 12.5, 16.4]</t>
+          <t>[7.7, 6.9, 5.4]</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13.87073009751796</v>
+        <v>6.048485054561561</v>
       </c>
       <c r="G23" t="n">
-        <v>13.18104280396016</v>
+        <v>4.437498895808005</v>
       </c>
       <c r="H23" t="n">
-        <v>91.43373248853396</v>
+        <v>61.23584194114184</v>
       </c>
     </row>
     <row r="24">
@@ -1290,32 +1290,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[31.79, 6.16, 4.88]</t>
+          <t>[5.38, 6.94, 33.65]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>[12.5, 16.4, 11.6]</t>
+          <t>[6.9, 5.4, 12.6]</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13.19235586993196</v>
+        <v>12.22005737080972</v>
       </c>
       <c r="G24" t="n">
-        <v>12.08336428296626</v>
+        <v>8.03901761101211</v>
       </c>
       <c r="H24" t="n">
-        <v>91.56489830690931</v>
+        <v>72.56346708055007</v>
       </c>
     </row>
     <row r="25">
@@ -1326,32 +1326,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[6.16, 4.88, 22.77]</t>
+          <t>[6.94, 33.65, 13.07]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[16.4, 11.6, 16.7]</t>
+          <t>[5.4, 12.6, 22.6]</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>7.890820715778514</v>
+        <v>13.37179189582499</v>
       </c>
       <c r="G25" t="n">
-        <v>7.675270618378974</v>
+        <v>10.70746432202846</v>
       </c>
       <c r="H25" t="n">
-        <v>52.23165800245977</v>
+        <v>79.26741334587254</v>
       </c>
     </row>
     <row r="26">
@@ -1362,32 +1362,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[4.88, 22.77, 10.01]</t>
+          <t>[33.65, 13.07, 8.07]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>[11.6, 16.7, 15.7]</t>
+          <t>[12.6, 22.6, 19.0]</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6.173647310193942</v>
+        <v>14.75929175223535</v>
       </c>
       <c r="G26" t="n">
-        <v>6.158914022740865</v>
+        <v>13.83721969740657</v>
       </c>
       <c r="H26" t="n">
-        <v>43.50122084193779</v>
+        <v>88.92649309444568</v>
       </c>
     </row>
     <row r="27">
@@ -1398,32 +1398,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[22.77, 10.01, 7.06]</t>
+          <t>[13.07, 8.07, 29.0]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>[16.7, 15.7, 24.0]</t>
+          <t>[22.6, 19.0, 8.2]</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10.89418254938119</v>
+        <v>14.64041207525907</v>
       </c>
       <c r="G27" t="n">
-        <v>9.56438519839258</v>
+        <v>13.75351588948382</v>
       </c>
       <c r="H27" t="n">
-        <v>47.71194239993608</v>
+        <v>117.7953015344317</v>
       </c>
     </row>
     <row r="28">
@@ -1434,32 +1434,32 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[10.01, 7.06, 17.95]</t>
+          <t>[8.07, 29.0, 6.83]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>[15.7, 24.0, 7.7]</t>
+          <t>[19.0, 8.2, 12.0]</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11.89244152723526</v>
+        <v>13.89326312197269</v>
       </c>
       <c r="G28" t="n">
-        <v>10.95859899999783</v>
+        <v>12.30291067679842</v>
       </c>
       <c r="H28" t="n">
-        <v>79.97115974955584</v>
+        <v>118.1180954296091</v>
       </c>
     </row>
     <row r="29">
@@ -1470,32 +1470,32 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[7.06, 17.95, 5.38]</t>
+          <t>[29.0, 6.83, 5.34]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>[24.0, 7.7, 6.9]</t>
+          <t>[8.2, 12.0, 40.7]</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11.46261073616588</v>
+        <v>23.87172706470043</v>
       </c>
       <c r="G29" t="n">
-        <v>9.568096086748227</v>
+        <v>20.44429742749375</v>
       </c>
       <c r="H29" t="n">
-        <v>75.22730360773036</v>
+        <v>127.8958283654078</v>
       </c>
     </row>
     <row r="30">
@@ -1506,32 +1506,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[17.95, 5.38, 6.94]</t>
+          <t>[6.83, 5.35, 22.08]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>[7.7, 6.9, 5.4]</t>
+          <t>[12.0, 40.7, 41.6]</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6.048485054561561</v>
+        <v>23.50832049921113</v>
       </c>
       <c r="G30" t="n">
-        <v>4.437498895808005</v>
+        <v>20.01754305926529</v>
       </c>
       <c r="H30" t="n">
-        <v>61.23584194114184</v>
+        <v>58.97106703166085</v>
       </c>
     </row>
     <row r="31">
@@ -1542,32 +1542,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[5.38, 6.94, 33.65]</t>
+          <t>[5.34, 22.08, 10.48]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[6.9, 5.4, 12.6]</t>
+          <t>[40.7, 41.6, 28.1]</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>12.22005737080972</v>
+        <v>25.44076860003979</v>
       </c>
       <c r="G31" t="n">
-        <v>8.03901761101211</v>
+        <v>24.1668926757567</v>
       </c>
       <c r="H31" t="n">
-        <v>72.56346708055007</v>
+        <v>65.50335015566162</v>
       </c>
     </row>
     <row r="32">
@@ -1578,32 +1578,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[317.21, 206.82, 497.21]</t>
+          <t>[157.78, 744.82, 744.4]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[323.81, 423.76, 441.9]</t>
+          <t>[133.5, 730.34, 709.68]</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>129.3113397729944</v>
+        <v>25.84999743331517</v>
       </c>
       <c r="G32" t="n">
-        <v>92.94860150090521</v>
+        <v>24.49448308119402</v>
       </c>
       <c r="H32" t="n">
-        <v>21.91579279934978</v>
+        <v>8.354717850689825</v>
       </c>
     </row>
     <row r="33">
@@ -1614,32 +1614,32 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>[207.14, 498.0, 186.47]</t>
+          <t>[735.41, 734.94, 537.37]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>[423.76, 441.9, 219.1]</t>
+          <t>[730.34, 709.68, 537.6]</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>130.5591981841522</v>
+        <v>14.87330503130768</v>
       </c>
       <c r="G33" t="n">
-        <v>101.7843028743277</v>
+        <v>10.18596473633852</v>
       </c>
       <c r="H33" t="n">
-        <v>26.23589479795154</v>
+        <v>1.431997094631216</v>
       </c>
     </row>
     <row r="34">
@@ -1650,32 +1650,32 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[528.08, 197.1, 458.87]</t>
+          <t>[734.56, 537.1, 1269.66]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>[441.9, 219.1, 487.69]</t>
+          <t>[709.68, 537.6, 930.28]</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>53.98294371790095</v>
+        <v>196.4694124185607</v>
       </c>
       <c r="G34" t="n">
-        <v>45.66988615212569</v>
+        <v>121.589186206505</v>
       </c>
       <c r="H34" t="n">
-        <v>11.81852785286619</v>
+        <v>13.36048147889665</v>
       </c>
     </row>
     <row r="35">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[193.79, 450.04, 443.93]</t>
+          <t>[535.73, 1266.51, 336.42]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>[219.1, 487.69, 446.9]</t>
+          <t>[537.6, 930.28, 322.1]</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>26.24633606647602</v>
+        <v>194.3009338480063</v>
       </c>
       <c r="G35" t="n">
-        <v>21.97403657637486</v>
+        <v>117.4698465061904</v>
       </c>
       <c r="H35" t="n">
-        <v>6.644899517568806</v>
+        <v>13.64467838864588</v>
       </c>
     </row>
     <row r="36">
@@ -1722,32 +1722,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[454.79, 448.68, 180.01]</t>
+          <t>[1266.84, 336.5, 364.7]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>[487.69, 446.9, 191.43]</t>
+          <t>[930.28, 322.1, 286.54]</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>20.13361321428696</v>
+        <v>199.6574690042055</v>
       </c>
       <c r="G36" t="n">
-        <v>15.36625500331247</v>
+        <v>143.0408238580586</v>
       </c>
       <c r="H36" t="n">
-        <v>4.370160088799694</v>
+        <v>22.64229472172426</v>
       </c>
     </row>
     <row r="37">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[451.79, 180.82, 157.05]</t>
+          <t>[328.97, 362.75, 446.53]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>[446.9, 191.43, 133.5]</t>
+          <t>[322.1, 286.54, 447.4]</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>15.1790658938511</v>
+        <v>44.18266913884348</v>
       </c>
       <c r="G37" t="n">
-        <v>13.01846652242187</v>
+        <v>27.98461301482081</v>
       </c>
       <c r="H37" t="n">
-        <v>8.093227319365951</v>
+        <v>9.641731832673571</v>
       </c>
     </row>
     <row r="38">
@@ -1794,32 +1794,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[180.68, 156.92, 741.43]</t>
+          <t>[362.21, 445.87, 208.42]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>[191.43, 133.5, 730.34]</t>
+          <t>[286.54, 447.4, 266.8]</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>16.19588582663026</v>
+        <v>55.18751213992567</v>
       </c>
       <c r="G38" t="n">
-        <v>15.0850456490465</v>
+        <v>45.19564642684975</v>
       </c>
       <c r="H38" t="n">
-        <v>8.22530783250817</v>
+        <v>16.21124374894737</v>
       </c>
     </row>
     <row r="39">
@@ -1830,32 +1830,32 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[157.78, 744.82, 744.4]</t>
+          <t>[442.49, 203.54, 456.5]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[133.5, 730.34, 709.68]</t>
+          <t>[447.4, 266.8, 496.55]</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>25.84999743331517</v>
+        <v>43.32190056063169</v>
       </c>
       <c r="G39" t="n">
-        <v>24.49448308119402</v>
+        <v>36.07643222671641</v>
       </c>
       <c r="H39" t="n">
-        <v>8.354717850689825</v>
+        <v>10.95856796215817</v>
       </c>
     </row>
     <row r="40">
@@ -1866,32 +1866,32 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[735.41, 734.94, 537.37]</t>
+          <t>[203.72, 456.92, 426.31]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>[730.34, 709.68, 537.6]</t>
+          <t>[266.8, 496.55, 688.0]</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14.87330503130768</v>
+        <v>157.090744537239</v>
       </c>
       <c r="G40" t="n">
-        <v>10.18596473633852</v>
+        <v>121.4687867022559</v>
       </c>
       <c r="H40" t="n">
-        <v>1.431997094631216</v>
+        <v>23.22088975948799</v>
       </c>
     </row>
     <row r="41">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>[734.56, 537.1, 1269.66]</t>
+          <t>[466.83, 435.18, 182.6]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>[709.68, 537.6, 930.28]</t>
+          <t>[496.55, 688.0, 212.7]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>196.4694124185607</v>
+        <v>147.9935432295808</v>
       </c>
       <c r="G41" t="n">
-        <v>121.589186206505</v>
+        <v>104.2122061481204</v>
       </c>
       <c r="H41" t="n">
-        <v>13.36048147889665</v>
+        <v>18.96099743927921</v>
       </c>
     </row>
     <row r="42">
@@ -1938,29 +1938,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>[-0.44, -0.44, -0.28]</t>
+          <t>[0.03, 0.72, 0.21]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.3923340644774982</v>
+        <v>0.4296466975383385</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3850091938835632</v>
+        <v>0.3140237809053524</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1976,29 +1976,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>[-0.39, -0.22, 0.03]</t>
+          <t>[0.71, 0.2, 0.96]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.8]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.5150300660425388</v>
+        <v>0.698784899182249</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4588665875828961</v>
+        <v>0.622089868840221</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2014,29 +2014,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>[-0.17, 0.09, -0.12]</t>
+          <t>[0.13, 0.84, 3.55]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>[0.0, 0.8, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.4263159552877642</v>
+        <v>2.114772534196791</v>
       </c>
       <c r="G44" t="n">
-        <v>0.3320343653973373</v>
+        <v>1.554847059180196</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -2052,29 +2052,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>[0.11, -0.1, 0.54]</t>
+          <t>[0.89, 3.67, -0.29]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>[0.8, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.5069044896329705</v>
+        <v>2.184353876389907</v>
       </c>
       <c r="G45" t="n">
-        <v>0.4421992018303616</v>
+        <v>1.614018920506459</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -2090,29 +2090,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>[-0.05, 0.63, -0.14]</t>
+          <t>[3.34, -0.34, -0.33]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.5]</t>
+          <t>[0.0, 0.0, 0.7]</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.5191132459556151</v>
+        <v>2.025698946808581</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4396085972907242</v>
+        <v>1.568543871448109</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -2128,29 +2128,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>[0.64, -0.14, 0.02]</t>
+          <t>[-0.45, -0.44, -0.3]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>[0.0, 0.5, 0.0]</t>
+          <t>[0.0, 0.7, 0.0]</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.5202152217863512</v>
+        <v>0.7288726493431285</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4308818553058438</v>
+        <v>0.6303436181731709</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -2166,29 +2166,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>[-0.18, -0.04, 0.6]</t>
+          <t>[-0.39, -0.25, 0.02]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>[0.5, 0.0, 0.0]</t>
+          <t>[0.7, 0.0, 2.9]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.5265957427019039</v>
+        <v>1.784968485572952</v>
       </c>
       <c r="G48" t="n">
-        <v>0.4413625696049108</v>
+        <v>1.407072668486667</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2204,29 +2204,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>[0.03, 0.72, 0.21]</t>
+          <t>[-0.15, 0.15, -0.11]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 2.9, 0.9]</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.4296466975383385</v>
+        <v>1.694077463687371</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3140237809053524</v>
+        <v>1.302907233388351</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2242,29 +2242,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>[0.71, 0.2, 0.96]</t>
+          <t>[0.17, -0.09, 0.47]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[2.9, 0.9, 0.0]</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.698784899182249</v>
+        <v>1.699753384402667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.622089868840221</v>
+        <v>1.399070989375208</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2280,29 +2280,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>[0.13, 0.84, 3.55]</t>
+          <t>[0.04, 0.68, -0.02]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.0]</t>
+          <t>[0.9, 0.0, 0.6]</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.114772534196791</v>
+        <v>0.72792397628145</v>
       </c>
       <c r="G51" t="n">
-        <v>1.554847059180196</v>
+        <v>0.7203306989139741</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.13, -0.0]</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.05598168377767723</v>
+        <v>0.07757260932218334</v>
       </c>
       <c r="G62" t="n">
-        <v>0.03232110607068189</v>
+        <v>0.04478684093149754</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2696,17 +2696,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0.1, 0.0, 0.0]</t>
+          <t>[0.13, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.05598283209720575</v>
+        <v>0.07756818687992217</v>
       </c>
       <c r="G63" t="n">
-        <v>0.03232224857570627</v>
+        <v>0.04478422039194671</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2734,17 +2734,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2753,10 +2753,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.556058017980695e-05</v>
+        <v>5.427789918467537e-09</v>
       </c>
       <c r="G64" t="n">
-        <v>1.555562334311278e-05</v>
+        <v>5.191664342946514e-09</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2772,17 +2772,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.12]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.07116544121606998</v>
+        <v>8.680381296779742e-08</v>
       </c>
       <c r="G65" t="n">
-        <v>0.04110648983816189</v>
+        <v>5.467350563984785e-08</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -2810,17 +2810,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[-0.0, 0.12, -0.0]</t>
+          <t>[0.0, 0.0, 0.09]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.07125342661872151</v>
+        <v>0.05014711797677458</v>
       </c>
       <c r="G66" t="n">
-        <v>0.0411406009208146</v>
+        <v>0.02895298081068998</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -2848,17 +2848,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0.12, 0.0, 0.0]</t>
+          <t>[0.0, 0.09, 0.0]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2867,10 +2867,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.07123781872060755</v>
+        <v>0.05014716311196819</v>
       </c>
       <c r="G67" t="n">
-        <v>0.04113329296787952</v>
+        <v>0.02895279065181896</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -2886,17 +2886,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.13]</t>
+          <t>[0.09, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.07757260019859284</v>
+        <v>0.05014794810899615</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0447867074853413</v>
+        <v>0.02895320652367391</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -2924,17 +2924,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>[0.0, 0.13, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.07757260932218334</v>
+        <v>4.504062700709355e-06</v>
       </c>
       <c r="G69" t="n">
-        <v>0.04478684093149754</v>
+        <v>4.503495367059186e-06</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2962,17 +2962,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>[0.13, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.11]</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.07756818687992217</v>
+        <v>0.06374450757009439</v>
       </c>
       <c r="G70" t="n">
-        <v>0.04478422039194671</v>
+        <v>0.03680676573034852</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -3000,17 +3000,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.11, 0.0]</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3019,10 +3019,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5.427789918467537e-09</v>
+        <v>0.06388104037985989</v>
       </c>
       <c r="G71" t="n">
-        <v>5.191664342946514e-09</v>
+        <v>0.03689099386919593</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -3038,12 +3038,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3378,32 +3378,32 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>[108.21, 31.59, 57.56]</t>
+          <t>[10.68, 93.23, 22.89]</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>[109.8, 32.3, 59.0]</t>
+          <t>[14.2, 98.5, 25.9]</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.304582639037492</v>
+        <v>4.051813696579853</v>
       </c>
       <c r="G82" t="n">
-        <v>1.246667555656645</v>
+        <v>3.933899642047002</v>
       </c>
       <c r="H82" t="n">
-        <v>2.028970568926046</v>
+        <v>13.91554905088792</v>
       </c>
     </row>
     <row r="83">
@@ -3414,32 +3414,32 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>[31.59, 57.56, 16.68]</t>
+          <t>[94.33, 22.78, 31.8]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>[32.3, 59.0, 17.1]</t>
+          <t>[98.5, 25.9, 33.6]</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.9581410986858767</v>
+        <v>3.179145768662143</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8566671267684486</v>
+        <v>3.028524160507416</v>
       </c>
       <c r="H83" t="n">
-        <v>2.36498810207245</v>
+        <v>7.208445823280699</v>
       </c>
     </row>
     <row r="84">
@@ -3450,32 +3450,32 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[57.56, 16.68, 14.41]</t>
+          <t>[22.69, 31.53, 5.87]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>[59.0, 17.1, 14.4]</t>
+          <t>[25.9, 33.6, 5.8]</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.866045134946042</v>
+        <v>2.202537057554222</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6233335816443191</v>
+        <v>1.780202044606627</v>
       </c>
       <c r="H84" t="n">
-        <v>1.655421131121184</v>
+        <v>6.567943234074216</v>
       </c>
     </row>
     <row r="85">
@@ -3486,32 +3486,32 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>[16.68, 14.41, 16.02]</t>
+          <t>[31.82, 5.96, 109.7]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>[17.1, 14.4, 23.74]</t>
+          <t>[33.6, 5.8, 109.8]</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4.463739229898745</v>
+        <v>1.032028727811527</v>
       </c>
       <c r="G85" t="n">
-        <v>2.716666716119866</v>
+        <v>0.6808894124733866</v>
       </c>
       <c r="H85" t="n">
-        <v>11.68151345199069</v>
+        <v>2.718858898498776</v>
       </c>
     </row>
     <row r="86">
@@ -3522,32 +3522,32 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[14.41, 16.02, 13.5]</t>
+          <t>[6.03, 109.61, 32.28]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>[14.4, 23.74, 14.3]</t>
+          <t>[5.8, 109.8, 36.4]</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4.481015648728862</v>
+        <v>2.386659451905761</v>
       </c>
       <c r="G86" t="n">
-        <v>2.843333374433668</v>
+        <v>1.516036486271091</v>
       </c>
       <c r="H86" t="n">
-        <v>12.72760187673344</v>
+        <v>5.174350614381185</v>
       </c>
     </row>
     <row r="87">
@@ -3558,32 +3558,32 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[16.02, 13.5, 10.73]</t>
+          <t>[109.68, 32.28, 58.93]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>[23.74, 14.3, 14.2]</t>
+          <t>[109.8, 36.4, 60.4]</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4.908472424743495</v>
+        <v>2.525674463043348</v>
       </c>
       <c r="G87" t="n">
-        <v>3.996666832524126</v>
+        <v>1.903898258716611</v>
       </c>
       <c r="H87" t="n">
-        <v>20.8499945051063</v>
+        <v>4.620005426670407</v>
       </c>
     </row>
     <row r="88">
@@ -3594,32 +3594,32 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[13.64, 10.69, 93.78]</t>
+          <t>[32.28, 58.93, 17.09]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>[14.3, 14.2, 98.5]</t>
+          <t>[36.4, 60.4, 18.2]</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3.416899902380894</v>
+        <v>2.604450274914628</v>
       </c>
       <c r="G88" t="n">
-        <v>2.963161436844141</v>
+        <v>2.23169130404189</v>
       </c>
       <c r="H88" t="n">
-        <v>11.37290662617646</v>
+        <v>6.611846429381356</v>
       </c>
     </row>
     <row r="89">
@@ -3630,32 +3630,32 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[10.68, 93.23, 22.89]</t>
+          <t>[58.93, 17.09, 14.39]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>[14.2, 98.5, 25.9]</t>
+          <t>[60.4, 18.2, 15.6]</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4.051813696579853</v>
+        <v>1.269752447643089</v>
       </c>
       <c r="G89" t="n">
-        <v>3.933899642047002</v>
+        <v>1.260760261811018</v>
       </c>
       <c r="H89" t="n">
-        <v>13.91554905088792</v>
+        <v>5.419790036437576</v>
       </c>
     </row>
     <row r="90">
@@ -3666,32 +3666,32 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[94.33, 22.78, 31.8]</t>
+          <t>[17.09, 14.39, 23.44]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>[98.5, 25.9, 33.6]</t>
+          <t>[18.2, 15.6, 19.7]</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3.179145768662143</v>
+        <v>2.355761147489488</v>
       </c>
       <c r="G90" t="n">
-        <v>3.028524160507416</v>
+        <v>2.017490638785123</v>
       </c>
       <c r="H90" t="n">
-        <v>7.208445823280699</v>
+        <v>10.93266565334603</v>
       </c>
     </row>
     <row r="91">
@@ -3702,32 +3702,32 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[22.69, 31.53, 5.87]</t>
+          <t>[14.39, 23.44, 14.28]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>[25.9, 33.6, 5.8]</t>
+          <t>[15.6, 19.7, 14.2]</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.202537057554222</v>
+        <v>2.268108616440262</v>
       </c>
       <c r="G91" t="n">
-        <v>1.780202044606627</v>
+        <v>1.673940944633149</v>
       </c>
       <c r="H91" t="n">
-        <v>6.567943234074216</v>
+        <v>9.084481910360591</v>
       </c>
     </row>
     <row r="92">
@@ -3738,32 +3738,32 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>[2.99, 11.1, 8.53]</t>
+          <t>[7.55, 26.34, 10.71]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>[2.4, 8.7, 9.5]</t>
+          <t>[6.4, 31.5, 13.3]</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.534571853150742</v>
+        <v>3.400581692410254</v>
       </c>
       <c r="G92" t="n">
-        <v>1.322746274696257</v>
+        <v>2.96737147943017</v>
       </c>
       <c r="H92" t="n">
-        <v>20.87305851298839</v>
+        <v>17.93491601366808</v>
       </c>
     </row>
     <row r="93">
@@ -3774,32 +3774,32 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>[11.02, 8.45, 1.51]</t>
+          <t>[26.1, 10.61, 2.38]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>[8.7, 9.5, 1.6]</t>
+          <t>[31.5, 13.3, 2.6]</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.470757053819533</v>
+        <v>3.48752242204997</v>
       </c>
       <c r="G93" t="n">
-        <v>1.152717007078093</v>
+        <v>2.772194269639559</v>
       </c>
       <c r="H93" t="n">
-        <v>14.42260238923023</v>
+        <v>15.29417853264547</v>
       </c>
     </row>
     <row r="94">
@@ -3810,32 +3810,32 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>[8.3, 1.48, 9.34]</t>
+          <t>[10.76, 2.41, 16.94]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>[9.5, 1.6, 9.3]</t>
+          <t>[13.3, 2.6, 18.4]</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.6959158369135364</v>
+        <v>1.696584455925857</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4508419967031572</v>
+        <v>1.396933233731958</v>
       </c>
       <c r="H94" t="n">
-        <v>6.798372691428929</v>
+        <v>11.43185451850302</v>
       </c>
     </row>
     <row r="95">
@@ -3846,32 +3846,32 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>[1.5, 9.41, 53.8]</t>
+          <t>[2.45, 17.11, 2.67]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>[1.6, 9.3, 58.0]</t>
+          <t>[2.6, 18.4, 2.5]</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2.426038986638272</v>
+        <v>0.7551713771905995</v>
       </c>
       <c r="G95" t="n">
-        <v>1.470291201718556</v>
+        <v>0.5366721568899222</v>
       </c>
       <c r="H95" t="n">
-        <v>4.913682931082936</v>
+        <v>6.547465176866766</v>
       </c>
     </row>
     <row r="96">
@@ -3882,32 +3882,32 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>[9.43, 53.93, 0.7]</t>
+          <t>[17.16, 2.68, 9.89]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>[9.3, 58.0, 0.6]</t>
+          <t>[18.4, 2.5, 8.7]</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.352380918328856</v>
+        <v>0.9952473575131359</v>
       </c>
       <c r="G96" t="n">
-        <v>1.434023141740838</v>
+        <v>0.8671908536847016</v>
       </c>
       <c r="H96" t="n">
-        <v>8.177701928646842</v>
+        <v>9.149913302160114</v>
       </c>
     </row>
     <row r="97">
@@ -3918,32 +3918,32 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[53.89, 0.7, 7.54]</t>
+          <t>[2.69, 9.93, 9.22]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>[58.0, 0.6, 6.4]</t>
+          <t>[2.5, 8.7, 9.7]</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2.464632961207342</v>
+        <v>0.7687678608349444</v>
       </c>
       <c r="G97" t="n">
-        <v>1.782813109943379</v>
+        <v>0.6336596496109842</v>
       </c>
       <c r="H97" t="n">
-        <v>13.59179849140467</v>
+        <v>8.924371853435805</v>
       </c>
     </row>
     <row r="98">
@@ -3954,32 +3954,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[0.7, 7.58, 26.41]</t>
+          <t>[9.89, 9.19, 1.6]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>[0.6, 6.4, 31.5]</t>
+          <t>[8.7, 9.7, 1.7]</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3.017789498380753</v>
+        <v>0.7517871840676837</v>
       </c>
       <c r="G98" t="n">
-        <v>2.123594033469586</v>
+        <v>0.6018117388134695</v>
       </c>
       <c r="H98" t="n">
-        <v>17.2195791305106</v>
+        <v>8.307372132379749</v>
       </c>
     </row>
     <row r="99">
@@ -3990,32 +3990,32 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[7.55, 26.34, 10.71]</t>
+          <t>[9.12, 1.58, 9.47]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>[6.4, 31.5, 13.3]</t>
+          <t>[9.7, 1.7, 9.6]</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3.400581692410254</v>
+        <v>0.3514345567716906</v>
       </c>
       <c r="G99" t="n">
-        <v>2.96737147943017</v>
+        <v>0.2771631071448242</v>
       </c>
       <c r="H99" t="n">
-        <v>17.93491601366808</v>
+        <v>4.776128473612733</v>
       </c>
     </row>
     <row r="100">
@@ -4026,32 +4026,32 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>[26.1, 10.61, 2.38]</t>
+          <t>[1.59, 9.5, 56.78]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>[31.5, 13.3, 2.6]</t>
+          <t>[1.7, 9.6, 59.92]</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3.48752242204997</v>
+        <v>1.817433420797602</v>
       </c>
       <c r="G100" t="n">
-        <v>2.772194269639559</v>
+        <v>1.117036920821803</v>
       </c>
       <c r="H100" t="n">
-        <v>15.29417853264547</v>
+        <v>4.242194242172452</v>
       </c>
     </row>
     <row r="101">
@@ -4062,32 +4062,32 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[10.76, 2.41, 16.94]</t>
+          <t>[9.53, 56.91, 0.66]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>[13.3, 2.6, 18.4]</t>
+          <t>[9.6, 59.92, 0.6]</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>1.696584455925857</v>
+        <v>1.736607758573169</v>
       </c>
       <c r="G101" t="n">
-        <v>1.396933233731958</v>
+        <v>1.046656585057107</v>
       </c>
       <c r="H101" t="n">
-        <v>11.43185451850302</v>
+        <v>5.369173040734454</v>
       </c>
     </row>
     <row r="102">
@@ -4098,29 +4098,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>[0.51, -0.0, 8.73]</t>
+          <t>[-0.0, 7.97, 0.66]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>[0.9, 0.0, 10.6]</t>
+          <t>[0.0, 9.2, 0.0]</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1.10287512839201</v>
+        <v>0.8059156351093955</v>
       </c>
       <c r="G102" t="n">
-        <v>0.7533334048383926</v>
+        <v>0.6300000047673081</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -4136,29 +4136,29 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[-0.0, 8.73, 1.98]</t>
+          <t>[7.97, 0.66, 1.15]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>[0.0, 10.6, 2.0]</t>
+          <t>[9.2, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>1.079706827638174</v>
+        <v>1.044190281655792</v>
       </c>
       <c r="G103" t="n">
-        <v>0.6300000613919948</v>
+        <v>1.013333337715808</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -4174,32 +4174,34 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>[8.73, 1.98, 6.2]</t>
+          <t>[0.66, 1.15, 15.59]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>[10.6, 2.0, 6.2]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1.079706827638174</v>
+        <v>9.033386307542482</v>
       </c>
       <c r="G104" t="n">
-        <v>0.630000068636047</v>
-      </c>
-      <c r="H104" t="n">
-        <v>6.213837682695373</v>
+        <v>5.800000050722663</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -4210,32 +4212,34 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>[1.98, 6.2, 7.3]</t>
+          <t>[1.15, 15.59, 0.9]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>[2.0, 6.2, 7.7]</t>
+          <t>[0.0, 0.0, 0.4]</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0.2312286131161012</v>
+        <v>9.029961251158111</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1400000208417054</v>
-      </c>
-      <c r="H105" t="n">
-        <v>2.064935691066185</v>
+        <v>5.746666667920237</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -4246,29 +4250,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>[6.2, 7.3, -0.0]</t>
+          <t>[15.59, 0.9, -0.0]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>[6.2, 7.7, 0.0]</t>
+          <t>[0.0, 0.4, 0.0]</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0.2309401169272298</v>
+        <v>9.005518580256698</v>
       </c>
       <c r="G106" t="n">
-        <v>0.1333333452213713</v>
+        <v>5.363333272841953</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -4284,29 +4288,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>[7.3, -0.0, -0.0]</t>
+          <t>[0.88, -0.01, 10.47]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>[7.7, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 9.8]</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.2309401169272296</v>
+        <v>0.4761550242592339</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1333333399616767</v>
+        <v>0.3870491392327937</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -4322,29 +4326,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 7.97]</t>
+          <t>[-0.02, 10.33, 1.93]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 9.2]</t>
+          <t>[0.0, 9.8, 2.0]</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.7101408389457649</v>
+        <v>0.3103560720795478</v>
       </c>
       <c r="G108" t="n">
-        <v>0.4100000053473667</v>
+        <v>0.2079956351302912</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -4360,34 +4364,32 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>[-0.0, 7.97, 0.66]</t>
+          <t>[10.34, 1.93, 6.04]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>[0.0, 9.2, 0.0]</t>
+          <t>[9.8, 2.0, 6.3]</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.8059156351093955</v>
+        <v>0.3500569858558269</v>
       </c>
       <c r="G109" t="n">
-        <v>0.6300000047673081</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.289886705241791</v>
+      </c>
+      <c r="H109" t="n">
+        <v>4.327992956631476</v>
       </c>
     </row>
     <row r="110">
@@ -4398,34 +4400,32 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>[7.97, 0.66, 1.15]</t>
+          <t>[1.93, 6.03, 7.49]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>[9.2, 0.0, 0.0]</t>
+          <t>[2.0, 6.3, 6.4]</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>1.044190281655792</v>
+        <v>0.648370975328413</v>
       </c>
       <c r="G110" t="n">
-        <v>1.013333337715808</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.4780147654587689</v>
+      </c>
+      <c r="H110" t="n">
+        <v>8.326067929741075</v>
       </c>
     </row>
     <row r="111">
@@ -4436,29 +4436,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>[0.66, 1.15, 15.59]</t>
+          <t>[6.03, 7.5, -0.02]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[6.3, 6.4, 0.0]</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>9.033386307542482</v>
+        <v>0.6513628282900876</v>
       </c>
       <c r="G111" t="n">
-        <v>5.800000050722663</v>
+        <v>0.4621316399192312</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4474,17 +4474,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>[-0.0, 0.04, 0.12]</t>
+          <t>[-0.0, 0.28, 0.04]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.07236498630213184</v>
+        <v>0.1650284108378911</v>
       </c>
       <c r="G112" t="n">
-        <v>0.0525015344664988</v>
+        <v>0.1071281815389084</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -4512,17 +4512,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>[0.04, 0.12, -0.0]</t>
+          <t>[0.28, 0.04, 0.04]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.07235920633522856</v>
+        <v>0.1664705968993791</v>
       </c>
       <c r="G113" t="n">
-        <v>0.05249492755540924</v>
+        <v>0.1198099037077421</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4550,29 +4550,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>[0.12, -0.0, -0.0]</t>
+          <t>[0.04, 0.04, 0.25]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.2]</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.06894246006065356</v>
+        <v>0.5521783862616833</v>
       </c>
       <c r="G114" t="n">
-        <v>0.03980394932851884</v>
+        <v>0.3436938268480146</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4588,29 +4588,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.31]</t>
+          <t>[0.04, 0.25, -0.0]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 1.2, 0.0]</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.1805885840191261</v>
+        <v>0.5517627495232725</v>
       </c>
       <c r="G115" t="n">
-        <v>0.1043288715679889</v>
+        <v>0.3310053586695013</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4626,29 +4626,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>[0.0, 0.31, 0.1]</t>
+          <t>[0.25, -0.0, 0.03]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.2, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.1900455481694839</v>
+        <v>0.5516596170152439</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1383590388996098</v>
+        <v>0.3297038339866624</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4664,17 +4664,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>[0.31, 0.1, 0.0]</t>
+          <t>[-0.0, 0.03, 0.11]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4683,10 +4683,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.1901763728893287</v>
+        <v>0.06472460652790486</v>
       </c>
       <c r="G117" t="n">
-        <v>0.138569675266929</v>
+        <v>0.04701965423450524</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -4702,17 +4702,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>[0.1, -0.0, 0.28]</t>
+          <t>[0.03, 0.11, -0.0]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.1738620207657555</v>
+        <v>0.06479125420858377</v>
       </c>
       <c r="G118" t="n">
-        <v>0.1284802870337642</v>
+        <v>0.04703256386252311</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -4740,17 +4740,17 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>[-0.0, 0.28, 0.04]</t>
+          <t>[0.11, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4759,10 +4759,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.1650284108378911</v>
+        <v>0.06171703610185581</v>
       </c>
       <c r="G119" t="n">
-        <v>0.1071281815389084</v>
+        <v>0.03563670006800098</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4778,17 +4778,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>[0.28, 0.04, 0.04]</t>
+          <t>[-0.0, -0.0, 0.28]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.1664705968993791</v>
+        <v>0.1603879736091508</v>
       </c>
       <c r="G120" t="n">
-        <v>0.1198099037077421</v>
+        <v>0.09265291477770392</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4816,29 +4816,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>[0.04, 0.04, 0.25]</t>
+          <t>[-0.0, 0.28, 0.09]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.2]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.5521783862616833</v>
+        <v>0.1688245941951444</v>
       </c>
       <c r="G121" t="n">
-        <v>0.3436938268480146</v>
+        <v>0.1230904136771213</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4854,32 +4854,32 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>[494.14, 449.93, 430.32]</t>
+          <t>[2.08, 4.3, 19.92]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>[369.4, 328.32, 354.71]</t>
+          <t>[3.82, 5.31, 41.1]</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>109.6429917536425</v>
+        <v>12.28143734059107</v>
       </c>
       <c r="G122" t="n">
-        <v>107.3182052049856</v>
+        <v>7.973790050071941</v>
       </c>
       <c r="H122" t="n">
-        <v>30.70757617996485</v>
+        <v>38.65853847449912</v>
       </c>
     </row>
     <row r="123">
@@ -4890,32 +4890,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>[438.8, 419.85, 21.98]</t>
+          <t>[4.53, 20.82, 393.12]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>[328.32, 354.71, 1.4]</t>
+          <t>[5.31, 41.1, 440.84]</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>74.99281036210954</v>
+        <v>29.93677085738391</v>
       </c>
       <c r="G123" t="n">
-        <v>65.39845198430504</v>
+        <v>22.92291255595487</v>
       </c>
       <c r="H123" t="n">
-        <v>507.2797914907438</v>
+        <v>24.9194833022277</v>
       </c>
     </row>
     <row r="124">
@@ -4926,32 +4926,32 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>[409.65, 21.43, 3.67]</t>
+          <t>[21.07, 397.63, 701.38]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>[354.71, 1.4, 0.89]</t>
+          <t>[41.1, 440.84, 1740.77]</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>33.79894260310666</v>
+        <v>600.719701794969</v>
       </c>
       <c r="G124" t="n">
-        <v>25.9144830437775</v>
+        <v>367.5415300991997</v>
       </c>
       <c r="H124" t="n">
-        <v>586.0106835674708</v>
+        <v>39.41129686061895</v>
       </c>
     </row>
     <row r="125">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[21.16, 3.61, 3.06]</t>
+          <t>[419.8, 740.16, 400.81]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>[1.4, 0.89, 2.32]</t>
+          <t>[440.84, 1740.77, 450.07]</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>11.52652922373131</v>
+        <v>578.5281536077979</v>
       </c>
       <c r="G125" t="n">
-        <v>7.74240219120025</v>
+        <v>356.9712601582017</v>
       </c>
       <c r="H125" t="n">
-        <v>583.1444713539736</v>
+        <v>24.39995699890946</v>
       </c>
     </row>
     <row r="126">
@@ -4998,32 +4998,32 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>[2.84, 2.39, 2.01]</t>
+          <t>[742.98, 402.3, 366.06]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>[0.89, 2.32, 1.9]</t>
+          <t>[1740.77, 450.07, 376.72]</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>1.128212503629148</v>
+        <v>576.7643366213113</v>
       </c>
       <c r="G126" t="n">
-        <v>0.7100452149003759</v>
+        <v>352.0729518066414</v>
       </c>
       <c r="H126" t="n">
-        <v>75.96976446441762</v>
+        <v>23.58772157512055</v>
       </c>
     </row>
     <row r="127">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>[2.16, 1.81, 2.06]</t>
+          <t>[430.89, 391.85, 379.82]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>[2.32, 1.9, 3.82]</t>
+          <t>[450.07, 376.72, 335.32]</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1.023753772128909</v>
+        <v>29.30832027102856</v>
       </c>
       <c r="G127" t="n">
-        <v>0.67286997759571</v>
+        <v>26.2700481551124</v>
       </c>
       <c r="H127" t="n">
-        <v>19.34825988337915</v>
+        <v>7.182823761138195</v>
       </c>
     </row>
     <row r="128">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>[1.82, 2.07, 4.29]</t>
+          <t>[393.25, 381.16, 15.94]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>[1.9, 3.82, 5.31]</t>
+          <t>[376.72, 335.32, 72.2]</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>1.16881740203931</v>
+        <v>42.9715491308997</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9480893557065536</v>
+        <v>39.54395059715905</v>
       </c>
       <c r="H128" t="n">
-        <v>22.99905144065188</v>
+        <v>31.99224149522875</v>
       </c>
     </row>
     <row r="129">
@@ -5106,32 +5106,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>[2.08, 4.3, 19.92]</t>
+          <t>[379.86, 15.89, 3.02]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>[3.82, 5.31, 41.1]</t>
+          <t>[335.32, 72.2, 1.51]</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>12.28143734059107</v>
+        <v>41.46176455282902</v>
       </c>
       <c r="G129" t="n">
-        <v>7.973790050071941</v>
+        <v>34.11971997591997</v>
       </c>
       <c r="H129" t="n">
-        <v>38.65853847449912</v>
+        <v>63.66629616828673</v>
       </c>
     </row>
     <row r="130">
@@ -5142,32 +5142,32 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>[4.53, 20.82, 393.12]</t>
+          <t>[15.72, 2.98, 2.76]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>[5.31, 41.1, 440.84]</t>
+          <t>[72.2, 1.51, 56.94]</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>29.93677085738391</v>
+        <v>45.19775306899702</v>
       </c>
       <c r="G130" t="n">
-        <v>22.92291255595487</v>
+        <v>37.37794970068797</v>
       </c>
       <c r="H130" t="n">
-        <v>24.9194833022277</v>
+        <v>90.15292981411146</v>
       </c>
     </row>
     <row r="131">
@@ -5178,32 +5178,32 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>[21.07, 397.63, 701.38]</t>
+          <t>[3.49, 3.23, 2.75]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>[41.1, 440.84, 1740.77]</t>
+          <t>[1.51, 56.94, 13.58]</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>600.719701794969</v>
+        <v>31.65216492171518</v>
       </c>
       <c r="G131" t="n">
-        <v>367.5415300991997</v>
+        <v>22.17164065153906</v>
       </c>
       <c r="H131" t="n">
-        <v>39.41129686061895</v>
+        <v>101.6762066861823</v>
       </c>
     </row>
     <row r="132">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>[192.05, 275.6, 35.92]</t>
+          <t>[188.21, 678.57, 267.74]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>[168.4, 304.5, 45.2]</t>
+          <t>[409.3, 901.6, 279.4]</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>22.2163694817191</v>
+        <v>181.4343128779722</v>
       </c>
       <c r="G132" t="n">
-        <v>20.61113712226102</v>
+        <v>151.9241445384716</v>
       </c>
       <c r="H132" t="n">
-        <v>14.69167174003084</v>
+        <v>27.64197188585249</v>
       </c>
     </row>
     <row r="133">
@@ -5250,32 +5250,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>[273.48, 35.64, 101.62]</t>
+          <t>[726.69, 286.55, 385.94]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>[304.5, 45.2, 333.5]</t>
+          <t>[901.6, 279.4, 326.2]</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>135.1825413300926</v>
+        <v>106.7915813470558</v>
       </c>
       <c r="G133" t="n">
-        <v>90.82161034678001</v>
+        <v>80.59962483746489</v>
       </c>
       <c r="H133" t="n">
-        <v>33.62425224863846</v>
+        <v>13.42424320516536</v>
       </c>
     </row>
     <row r="134">
@@ -5286,32 +5286,32 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>[35.86, 102.24, 159.67]</t>
+          <t>[293.73, 395.53, 546.0]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>[45.2, 333.5, 145.3]</t>
+          <t>[279.4, 326.2, 921.4]</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>133.8813105160269</v>
+        <v>220.5567440507257</v>
       </c>
       <c r="G134" t="n">
-        <v>84.9860480590883</v>
+        <v>153.0217604311205</v>
       </c>
       <c r="H134" t="n">
-        <v>33.29537885668714</v>
+        <v>22.3757967454364</v>
       </c>
     </row>
     <row r="135">
@@ -5322,32 +5322,32 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>[103.61, 161.77, 270.99]</t>
+          <t>[393.26, 542.95, 223.4]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>[333.5, 145.3, 316.0]</t>
+          <t>[326.2, 921.4, 164.0]</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>135.5797131798584</v>
+        <v>224.5366253931305</v>
       </c>
       <c r="G135" t="n">
-        <v>97.12389735733659</v>
+        <v>168.3029298949146</v>
       </c>
       <c r="H135" t="n">
-        <v>31.50448934340446</v>
+        <v>32.61674953323863</v>
       </c>
     </row>
     <row r="136">
@@ -5358,32 +5358,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>[174.85, 292.6, 160.81]</t>
+          <t>[532.67, 219.11, 321.2]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>[145.3, 316.0, 165.2]</t>
+          <t>[921.4, 164.0, 580.5]</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>21.91232419537042</v>
+        <v>271.6514355137396</v>
       </c>
       <c r="G136" t="n">
-        <v>19.11733405904661</v>
+        <v>234.3777668091645</v>
       </c>
       <c r="H136" t="n">
-        <v>10.13529011921743</v>
+        <v>40.15262553417662</v>
       </c>
     </row>
     <row r="137">
@@ -5394,32 +5394,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>[249.29, 137.39, 162.29]</t>
+          <t>[231.56, 339.27, 44.9]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>[316.0, 165.2, 409.3]</t>
+          <t>[164.0, 580.5, 109.58]</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>148.5924938972056</v>
+        <v>149.3739649839018</v>
       </c>
       <c r="G137" t="n">
-        <v>113.8430485047319</v>
+        <v>124.4879691348329</v>
       </c>
       <c r="H137" t="n">
-        <v>32.76412928412074</v>
+        <v>47.25812793091836</v>
       </c>
     </row>
     <row r="138">
@@ -5430,32 +5430,32 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>[159.41, 187.7, 676.67]</t>
+          <t>[326.72, 43.22, 134.95]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>[165.2, 409.3, 901.6]</t>
+          <t>[580.5, 109.58, 94.7]</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>182.3307697018908</v>
+        <v>153.2213193277636</v>
       </c>
       <c r="G138" t="n">
-        <v>150.7725356747588</v>
+        <v>120.1317389296292</v>
       </c>
       <c r="H138" t="n">
-        <v>27.53089750121523</v>
+        <v>48.92670939997303</v>
       </c>
     </row>
     <row r="139">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>[188.21, 678.57, 267.74]</t>
+          <t>[45.83, 142.91, 195.82]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>[409.3, 901.6, 279.4]</t>
+          <t>[109.58, 94.7, 174.45]</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>181.4343128779722</v>
+        <v>47.76491229360832</v>
       </c>
       <c r="G139" t="n">
-        <v>151.9241445384716</v>
+        <v>44.4418224301803</v>
       </c>
       <c r="H139" t="n">
-        <v>27.64197188585249</v>
+        <v>40.44355723012962</v>
       </c>
     </row>
     <row r="140">
@@ -5502,32 +5502,32 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>[726.69, 286.55, 385.94]</t>
+          <t>[158.99, 217.6, 372.75]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>[901.6, 279.4, 326.2]</t>
+          <t>[94.7, 174.45, 317.85]</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>106.7915813470558</v>
+        <v>54.79953142035311</v>
       </c>
       <c r="G140" t="n">
-        <v>80.59962483746489</v>
+        <v>54.11277247324303</v>
       </c>
       <c r="H140" t="n">
-        <v>13.42424320516536</v>
+        <v>36.6313602099978</v>
       </c>
     </row>
     <row r="141">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>[293.73, 395.53, 546.0]</t>
+          <t>[202.94, 347.91, 190.02]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>[279.4, 326.2, 921.4]</t>
+          <t>[174.45, 317.85, 163.8]</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>220.5567440507257</v>
+        <v>28.30015449150817</v>
       </c>
       <c r="G141" t="n">
-        <v>153.0217604311205</v>
+        <v>28.25632405574669</v>
       </c>
       <c r="H141" t="n">
-        <v>22.3757967454364</v>
+        <v>13.93218745321545</v>
       </c>
     </row>
     <row r="142">
@@ -5574,29 +5574,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>[2.47, -0.2, -0.19]</t>
+          <t>[-0.19, -0.17, -0.16]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>[1.68, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.7]</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.4849425686403306</v>
+        <v>0.5172930726287428</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3944474359362816</v>
+        <v>0.4058621975334716</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -5612,29 +5612,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>[-0.25, -0.23, -0.22]</t>
+          <t>[-0.14, -0.12, 1.3]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.7, 1.4]</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.2350259222669638</v>
+        <v>0.4863371524933049</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2347282055081523</v>
+        <v>0.354569631116764</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5650,34 +5650,32 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>[-0.19, -0.17, -0.16]</t>
+          <t>[-0.1, 1.37, 7.09]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.7]</t>
+          <t>[0.7, 1.4, 17.1]</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.5172930726287428</v>
+        <v>5.795786813581452</v>
       </c>
       <c r="G144" t="n">
-        <v>0.4058621975334716</v>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>3.611402219021013</v>
+      </c>
+      <c r="H144" t="n">
+        <v>58.17012249145056</v>
       </c>
     </row>
     <row r="145">
@@ -5688,34 +5686,32 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>[-0.14, -0.12, 1.3]</t>
+          <t>[1.82, 8.57, 0.1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>[0.0, 0.7, 1.4]</t>
+          <t>[1.4, 17.1, 5.25]</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0.4863371524933049</v>
+        <v>5.757037850659739</v>
       </c>
       <c r="G145" t="n">
-        <v>0.354569631116764</v>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>4.697894001151526</v>
+      </c>
+      <c r="H145" t="n">
+        <v>59.22823158665879</v>
       </c>
     </row>
     <row r="146">
@@ -5726,65 +5722,65 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>[-0.1, 1.37, 7.09]</t>
+          <t>[8.06, 0.05, 0.06]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>[0.7, 1.4, 17.1]</t>
+          <t>[17.1, 5.25, 1.4]</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>5.795786813581452</v>
+        <v>6.071342789991268</v>
       </c>
       <c r="G146" t="n">
-        <v>3.611402219021013</v>
+        <v>5.195226626804301</v>
       </c>
       <c r="H146" t="n">
-        <v>58.17012249145056</v>
+        <v>82.64388575276169</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>[6.96, 0.0, 1.28]</t>
+          <t>[0.3, 0.3, 0.31]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>[37.8, 0.0, 4.3]</t>
+          <t>[5.25, 1.4, 0.0]</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>17.89204323138707</v>
+        <v>2.932510236254479</v>
       </c>
       <c r="G147" t="n">
-        <v>11.28606655110488</v>
+        <v>2.117547189175727</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5795,34 +5791,34 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>[1.3, 3.94, 2.94]</t>
+          <t>[5.03, 4.81, 4.61]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>[0.0, 4.3, 1.2]</t>
+          <t>[1.4, 0.0, 0.35]</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>1.269720978476091</v>
+        <v>4.260745291888449</v>
       </c>
       <c r="G148" t="n">
-        <v>1.133247631611491</v>
+        <v>4.233141488482902</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5833,34 +5829,34 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>[2.48, 1.84, 0.4]</t>
+          <t>[1.66, 1.6, 1.55]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>[4.3, 1.2, 0.0]</t>
+          <t>[0.0, 0.35, 0.0]</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>1.136847608547189</v>
+        <v>1.496646673734295</v>
       </c>
       <c r="G149" t="n">
-        <v>0.9529643030327614</v>
+        <v>1.486910065580061</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5871,34 +5867,34 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>[2.2, 0.58, 1.89]</t>
+          <t>[0.03, 0.06, 2.14]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>[1.2, 0.0, 2.7]</t>
+          <t>[0.35, 0.0, 3.98]</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.8147245344675034</v>
+        <v>1.076675635742268</v>
       </c>
       <c r="G150" t="n">
-        <v>0.7957571170138745</v>
+        <v>0.7388034031949107</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5909,34 +5905,34 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ЖЕТІСУ</t>
+          <t>ОБЛАСТЬ АБАЙ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[0.42, 1.62, 5.15]</t>
+          <t>[0.38, 3.04, 0.09]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[0.0, 2.7, 1.9]</t>
+          <t>[0.0, 3.98, 0.0]</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>1.991710401837264</v>
+        <v>0.5878582068862861</v>
       </c>
       <c r="G151" t="n">
-        <v>1.583318158806732</v>
+        <v>0.4700420059673489</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5947,34 +5943,34 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[2.48, 1.84, 0.4]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[4.3, 1.2, 0.0]</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>4.161709504274489e-05</v>
+        <v>1.136847608547189</v>
       </c>
       <c r="G152" t="n">
-        <v>3.886448834684321e-05</v>
+        <v>0.9529643030327614</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5985,34 +5981,34 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[2.2, 0.58, 1.89]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.2, 0.0, 2.7]</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>5.113956343233481e-05</v>
+        <v>0.8147245344675034</v>
       </c>
       <c r="G153" t="n">
-        <v>4.458267320398538e-05</v>
+        <v>0.7957571170138745</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -6023,34 +6019,34 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.42, 1.62, 5.15]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 2.7, 1.9]</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>2.213894148417475e-05</v>
+        <v>1.991710401837264</v>
       </c>
       <c r="G154" t="n">
-        <v>1.933014504968642e-05</v>
+        <v>1.583318158806732</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -6061,34 +6057,34 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[1.39, 4.64, 0.15]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[2.7, 1.9, 0.0]</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>4.011636644617425e-05</v>
+        <v>1.755571664875616</v>
       </c>
       <c r="G155" t="n">
-        <v>3.305097302082548e-05</v>
+        <v>1.400156679363399</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -6099,34 +6095,34 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.18]</t>
+          <t>[5.3, 0.28, 0.57]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.9, 0.0, 0.4]</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.1057759993363881</v>
+        <v>1.97248954565949</v>
       </c>
       <c r="G156" t="n">
-        <v>0.0611015423051138</v>
+        <v>1.284578911048332</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -6137,34 +6133,34 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[0.17, 0.06, 0.08]</t>
+          <t>[0.06, 0.31, 12.69]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[0.0, 0.42, 0.0]</t>
+          <t>[0.0, 0.4, 1.1]</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.2316329582587344</v>
+        <v>6.691519800214646</v>
       </c>
       <c r="G157" t="n">
-        <v>0.2009391460901724</v>
+        <v>3.914308492622905</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -6175,34 +6171,34 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[0.06, 0.08, 0.39]</t>
+          <t>[0.29, 12.46, -0.06]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[0.42, 0.0, 0.0]</t>
+          <t>[0.4, 1.1, 0.0]</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.3087471482506313</v>
+        <v>6.561283664955966</v>
       </c>
       <c r="G158" t="n">
-        <v>0.2756571343746411</v>
+        <v>3.84388667613325</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -6213,34 +6209,34 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[0.08, 0.39, 0.08]</t>
+          <t>[12.77, -0.04, -0.07]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.1, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.2346601121646793</v>
+        <v>6.737201900363236</v>
       </c>
       <c r="G159" t="n">
-        <v>0.1825171180531981</v>
+        <v>3.923825856449626</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -6251,34 +6247,34 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[0.39, 0.08, 0.09]</t>
+          <t>[0.0, 0.0, 12.49]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 28.3]</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0.2361408571866261</v>
+        <v>9.126042978904159</v>
       </c>
       <c r="G160" t="n">
-        <v>0.1864477625116212</v>
+        <v>5.268938454161636</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -6289,34 +6285,34 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ЖЕТІСУ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[0.08, 0.09, 0.0]</t>
+          <t>[0.0, 12.49, 0.0]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 28.3, 0.0]</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>0.06889352248074791</v>
+        <v>9.125445839678667</v>
       </c>
       <c r="G161" t="n">
-        <v>0.05604583755099046</v>
+        <v>5.268596781025872</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -6327,34 +6323,34 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[0.09, -0.0, 0.07]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.4]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>0.1998607764974082</v>
+        <v>2.213894148417475e-05</v>
       </c>
       <c r="G162" t="n">
-        <v>0.1418386206020209</v>
+        <v>1.933014504968642e-05</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -6365,34 +6361,34 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[-0.0, 0.07, 0.13]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>[0.0, 0.4, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.2060226387203895</v>
+        <v>4.011636644617425e-05</v>
       </c>
       <c r="G163" t="n">
-        <v>0.1533089730932372</v>
+        <v>3.305097302082548e-05</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -6403,34 +6399,34 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>[0.07, 0.13, -0.0]</t>
+          <t>[-0.0, -0.0, 0.18]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>[0.4, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.2059955269608099</v>
+        <v>0.1057759993363881</v>
       </c>
       <c r="G164" t="n">
-        <v>0.1532896079132799</v>
+        <v>0.0611015423051138</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -6441,22 +6437,22 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[0.13, -0.0, 0.15]</t>
+          <t>[-0.0, 0.18, 0.0]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6465,10 +6461,10 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.114322623639481</v>
+        <v>0.1057380332831417</v>
       </c>
       <c r="G165" t="n">
-        <v>0.09292115250341508</v>
+        <v>0.06107130367145692</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -6479,22 +6475,22 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[-0.0, 0.15, 0.38]</t>
+          <t>[0.18, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6503,10 +6499,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.238386251576103</v>
+        <v>0.1058796354055826</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1787720618724248</v>
+        <v>0.0611473457801566</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -6517,22 +6513,22 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[0.0, 0.08, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6541,10 +6537,10 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.04488429137143678</v>
+        <v>1.285428339363907e-09</v>
       </c>
       <c r="G167" t="n">
-        <v>0.02598574204778821</v>
+        <v>1.285428339332493e-09</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -6555,22 +6551,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[0.08, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6579,10 +6575,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.04482666827552537</v>
+        <v>1.285960879798545e-09</v>
       </c>
       <c r="G168" t="n">
-        <v>0.02588412581837546</v>
+        <v>1.285960879778734e-09</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -6593,22 +6589,22 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6617,10 +6613,10 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>3.79745420682252e-05</v>
+        <v>1.286402381960729e-09</v>
       </c>
       <c r="G169" t="n">
-        <v>2.989475572413478e-05</v>
+        <v>1.286402381937073e-09</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -6631,22 +6627,22 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6655,10 +6651,10 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>5.88648167879267e-06</v>
+        <v>1.050808240648811e-09</v>
       </c>
       <c r="G170" t="n">
-        <v>4.484266668778612e-06</v>
+        <v>8.688845586572792e-10</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -6669,22 +6665,22 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ОБЛАСТЬ ҰЛЫТАУ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.06]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6693,10 +6689,10 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0.03508341104682153</v>
+        <v>7.436734323253163e-10</v>
       </c>
       <c r="G171" t="n">
-        <v>0.02029038680788842</v>
+        <v>4.535099631026662e-10</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -6707,34 +6703,34 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[0.0, 0.06, -0.0]</t>
+          <t>[0.07, 0.13, -0.0]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.4, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.03506787313963629</v>
+        <v>0.2059955269608099</v>
       </c>
       <c r="G172" t="n">
-        <v>0.02025181231951508</v>
+        <v>0.1532896079132799</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -6745,22 +6741,22 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[0.06, 0.0, 0.13]</t>
+          <t>[0.13, -0.0, 0.15]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6769,10 +6765,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.08047493779907408</v>
+        <v>0.114322623639481</v>
       </c>
       <c r="G173" t="n">
-        <v>0.06205707536916888</v>
+        <v>0.09292115250341508</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -6783,22 +6779,22 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>[-0.01, 0.11, -0.01]</t>
+          <t>[-0.0, 0.15, 0.38]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6807,10 +6803,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.06567338201210168</v>
+        <v>0.238386251576103</v>
       </c>
       <c r="G174" t="n">
-        <v>0.04533182369272007</v>
+        <v>0.1787720618724248</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6821,22 +6817,22 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[0.11, -0.01, -0.01]</t>
+          <t>[0.15, 0.38, 0.15]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6845,10 +6841,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.06642290634973456</v>
+        <v>0.2534137379014241</v>
       </c>
       <c r="G175" t="n">
-        <v>0.04488336785196228</v>
+        <v>0.2284328800418169</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6859,22 +6855,22 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[-0.02, -0.02, 0.04]</t>
+          <t>[0.38, 0.15, 0.1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6883,10 +6879,10 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0.0280819079881053</v>
+        <v>0.2442121297136107</v>
       </c>
       <c r="G176" t="n">
-        <v>0.02697173217138232</v>
+        <v>0.2095695911556241</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6897,361 +6893,931 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[79.92, 71.71, 108.55]</t>
+          <t>[0.15, 0.1, 0.07]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>[67.86, 55.34, 88.6]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>16.44582585736959</v>
+        <v>0.1102816010332527</v>
       </c>
       <c r="G177" t="n">
-        <v>16.12664412363156</v>
-      </c>
-      <c r="H177" t="n">
-        <v>23.28964457027577</v>
+        <v>0.1054191280484305</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[68.88, 104.36, 89.46]</t>
+          <t>[0.1, 0.07, 0.35]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>[55.34, 88.6, 104.94]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>14.96034472106781</v>
+        <v>0.2112670838344396</v>
       </c>
       <c r="G178" t="n">
-        <v>14.92786944201688</v>
-      </c>
-      <c r="H178" t="n">
-        <v>19.00468055876465</v>
+        <v>0.1710019947713539</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[98.4, 84.41, 92.8]</t>
+          <t>[0.07, 0.35, 0.07]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[88.6, 104.94, 96.62]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>13.31474855541091</v>
+        <v>0.2077537519437938</v>
       </c>
       <c r="G179" t="n">
-        <v>11.38007415226947</v>
-      </c>
-      <c r="H179" t="n">
-        <v>11.52265329950773</v>
+        <v>0.1620453076872788</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[81.83, 90.0, 92.06]</t>
+          <t>[0.35, 0.07, 0.08]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[104.94, 96.62, 103.21]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>15.30163167887098</v>
+        <v>0.2090343937883153</v>
       </c>
       <c r="G180" t="n">
-        <v>13.62776939417316</v>
-      </c>
-      <c r="H180" t="n">
-        <v>13.22665927136011</v>
+        <v>0.1654905853385651</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>ПАВЛОДАРСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[96.09, 98.21, 41.9]</t>
+          <t>[0.02, 0.03, -0.04]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[96.62, 103.21, 38.88]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>3.386838470374135</v>
+        <v>0.03409037804258486</v>
       </c>
       <c r="G181" t="n">
-        <v>2.849840906088671</v>
-      </c>
-      <c r="H181" t="n">
-        <v>4.385843464175395</v>
+        <v>0.03261213369567801</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[98.32, 41.95, 196.96]</t>
+          <t>[-0.01, 0.11, -0.01]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>[103.21, 38.88, 142.22]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>31.77712982173902</v>
+        <v>0.06567338201210168</v>
       </c>
       <c r="G182" t="n">
-        <v>20.8979957987396</v>
-      </c>
-      <c r="H182" t="n">
-        <v>17.03810000270555</v>
+        <v>0.04533182369272007</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[42.41, 199.07, 97.95]</t>
+          <t>[0.11, -0.01, -0.01]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>[38.88, 142.22, 138.52]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>40.37380105006314</v>
+        <v>0.06642290634973456</v>
       </c>
       <c r="G183" t="n">
-        <v>33.65052757050598</v>
-      </c>
-      <c r="H183" t="n">
-        <v>26.11530802943601</v>
+        <v>0.04488336785196228</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[195.37, 96.14, 126.25]</t>
+          <t>[-0.02, -0.02, 0.04]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>[142.22, 138.52, 135.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>39.57559348632277</v>
+        <v>0.0280819079881053</v>
       </c>
       <c r="G184" t="n">
-        <v>34.79144556236782</v>
-      </c>
-      <c r="H184" t="n">
-        <v>24.83774168445237</v>
+        <v>0.02697173217138232</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[89.35, 117.46, 198.48]</t>
+          <t>[-0.02, 0.04, -0.02]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>[138.52, 135.1, 262.18]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>47.56504523622064</v>
+        <v>0.02761567493456677</v>
       </c>
       <c r="G185" t="n">
-        <v>43.50468488127782</v>
-      </c>
-      <c r="H185" t="n">
-        <v>24.28379696304633</v>
+        <v>0.0254691594362212</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>[0.04, -0.01, 0.05]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>0.04041385709521308</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0.03700780956320662</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>[-0.02, 0.05, -0.02]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>0.03246537379980875</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.02908905242668923</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>[0.05, -0.02, -0.02]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>0.03270546925209206</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0.02856124437727443</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>[-0.02, -0.02, -0.02]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>0.0215948004216988</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0215947932412723</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>[-0.02, -0.02, -0.02]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>0.0195881811426689</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.0195881775858004</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>СЕВЕРО-КАЗАХСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>[-0.02, -0.02, 0.04]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>[0.0, 0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>0.02521135506294021</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.02379751927933262</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>[195.37, 96.14, 126.25]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>[142.22, 138.52, 135.1]</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>39.57559348632277</v>
+      </c>
+      <c r="G192" t="n">
+        <v>34.79144556236782</v>
+      </c>
+      <c r="H192" t="n">
+        <v>24.83774168445237</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>[89.35, 117.46, 198.48]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>[138.52, 135.1, 262.18]</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>47.56504523622064</v>
+      </c>
+      <c r="G193" t="n">
+        <v>43.50468488127782</v>
+      </c>
+      <c r="H193" t="n">
+        <v>24.28379696304633</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>[129.3, 218.09, 356.65]</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>[135.1, 262.18, 764.44]</t>
         </is>
       </c>
-      <c r="F186" t="n">
+      <c r="F194" t="n">
         <v>236.8353890523368</v>
       </c>
-      <c r="G186" t="n">
+      <c r="G194" t="n">
         <v>152.5607001651811</v>
       </c>
-      <c r="H186" t="n">
+      <c r="H194" t="n">
         <v>24.81856847379931</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>[219.88, 359.52, 75.52]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>[262.18, 764.44, 69.2]</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>235.0829939914741</v>
+      </c>
+      <c r="G195" t="n">
+        <v>151.1828872516254</v>
+      </c>
+      <c r="H195" t="n">
+        <v>26.08110987885953</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>[371.73, 78.08, 68.96]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>[764.44, 69.2, 60.13]</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>226.8464454720516</v>
+      </c>
+      <c r="G196" t="n">
+        <v>136.8065496574644</v>
+      </c>
+      <c r="H196" t="n">
+        <v>26.29609708262291</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>[94.74, 83.49, 127.14]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>[69.2, 60.13, 93.1]</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>28.02782494309651</v>
+      </c>
+      <c r="G197" t="n">
+        <v>27.64626921568371</v>
+      </c>
+      <c r="H197" t="n">
+        <v>37.43882170409913</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>[74.76, 114.06, 103.04]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>[60.13, 93.1, 85.8]</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>17.80135159081901</v>
+      </c>
+      <c r="G198" t="n">
+        <v>17.6110427005741</v>
+      </c>
+      <c r="H198" t="n">
+        <v>22.3138730019994</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>[109.41, 98.89, 105.34]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>[93.1, 85.8, 96.61]</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>13.08370299439389</v>
+      </c>
+      <c r="G199" t="n">
+        <v>12.71037413862369</v>
+      </c>
+      <c r="H199" t="n">
+        <v>13.93749825519408</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>[96.43, 102.75, 105.66]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>[85.8, 96.61, 105.0]</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>7.100120968997337</v>
+      </c>
+      <c r="G200" t="n">
+        <v>5.812307123204107</v>
+      </c>
+      <c r="H200" t="n">
+        <v>6.460247034785771</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>ТУРКЕСТАНСКАЯ ОБЛАСТЬ</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>[101.01, 103.84, 43.52]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>[96.61, 105.0, 44.1]</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>2.646025126117475</v>
+      </c>
+      <c r="G201" t="n">
+        <v>2.043846856135969</v>
+      </c>
+      <c r="H201" t="n">
+        <v>2.321396359434658</v>
       </c>
     </row>
   </sheetData>
